--- a/InputData/elec/GHESS/Green Hydrogen Electricity Supply Shareweights.xlsx
+++ b/InputData/elec/GHESS/Green Hydrogen Electricity Supply Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\GHESS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\elec\GHESS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E51E6-BA89-4879-AFE0-0753A63A9214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E5077C-1884-442E-BF69-BFE9DE4EEB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
-  <si>
-    <t>Max Fraction of Production (dimensionless)</t>
-  </si>
   <si>
     <t>hard coal</t>
   </si>
@@ -134,6 +131,9 @@
   </si>
   <si>
     <t>GHESS Green Hydrogen Electricity Supply Shareweights</t>
+  </si>
+  <si>
+    <t>Shareweight (dimensionless)</t>
   </si>
 </sst>
 </file>
@@ -1218,27 +1218,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -1246,22 +1246,22 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1281,9 +1281,9 @@
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2328,7 +2328,7 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2993,7 +2993,7 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3088,7 +3088,7 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>0</v>
